--- a/public/templates/examples/A-094-PrivilegeReviewRecords-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-094-PrivilegeReviewRecords-EXAMPLE-L.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="0"/>
   <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
@@ -296,7 +296,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="800100" cy="800100"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -435,12 +435,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/examples/A-094-PrivilegeReviewRecords-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-094-PrivilegeReviewRecords-EXAMPLE-L.xlsx
@@ -664,7 +664,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="16" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="78" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Review period / Scope</t>
@@ -673,7 +673,7 @@
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Covers quarterly least-privilege reviews of identity-platform roles across all systems against the RBAC Documentation and Access Entitlement Matrix.  Review cadence: quarterly.  Reviewer (role): Information Security Analyst.</t>
+          <t>Covers quarterly least-privilege / entitlement-conformance reviews of identity-platform roles across all systems, covering every account type including privileged, against the RBAC Documentation and Access Entitlement Matrix. Privileged-account usage and session-monitoring reviews are recorded in the Privileged Access Review Records; account certification in the Periodic Account Review / Certification Records.  Review cadence: quarterly.  Reviewer (role): Information Security Analyst.</t>
         </is>
       </c>
       <c r="D7" s="17" t="n"/>

--- a/public/templates/examples/A-094-PrivilegeReviewRecords-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-094-PrivilegeReviewRecords-EXAMPLE-L.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Aptos"/>
@@ -162,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -211,6 +216,10 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -664,7 +673,7 @@
       <c r="E6" s="17" t="n"/>
       <c r="F6" s="16" t="n"/>
     </row>
-    <row r="7" ht="78" customHeight="1">
+    <row r="7" ht="82.2" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Review period / Scope</t>
@@ -722,7 +731,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>001</t>
@@ -754,7 +763,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>002</t>
@@ -860,7 +869,7 @@
     <row r="24" ht="29.75" customHeight="1">
       <c r="A24" s="8" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="34.7" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Automated quarterly reviews against the identity platform found two stale accounts (revoked) and one over-privileged role (reduced to least privilege). Results fed the finding register.</t>
@@ -898,7 +907,7 @@
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="12" t="n"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
+    <row r="29" ht="82.2" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Reviewed by (Information Security Analyst)</t>
@@ -914,10 +923,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
+      <c r="D29" s="21">
+        <v>46122</v>
       </c>
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
@@ -938,10 +945,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
+      <c r="D30" s="21">
+        <v>46122</v>
       </c>
       <c r="E30" s="13" t="n"/>
       <c r="F30" s="13" t="n"/>
@@ -1038,10 +1043,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="B46" s="20">
+        <v>46042</v>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
@@ -1093,7 +1096,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>